--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.89928425715445</v>
+        <v>8.433633691787598</v>
       </c>
       <c r="D2" t="n">
-        <v>21.02277954685844</v>
+        <v>3.416201676364497</v>
       </c>
       <c r="E2" t="n">
-        <v>12.55136630670771</v>
+        <v>2.039597024840003</v>
       </c>
       <c r="F2" t="n">
-        <v>10.059319468956</v>
+        <v>1.63463941370535</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.29717152739953</v>
+        <v>8.823290373202425</v>
       </c>
       <c r="D3" t="n">
-        <v>14.3818583381746</v>
+        <v>2.337051979953372</v>
       </c>
       <c r="E3" t="n">
-        <v>12.55136630670771</v>
+        <v>2.039597024840003</v>
       </c>
       <c r="F3" t="n">
-        <v>10.059319468956</v>
+        <v>1.63463941370535</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.6332922721382</v>
+        <v>7.577909994222457</v>
       </c>
       <c r="D4" t="n">
-        <v>40.38649688527779</v>
+        <v>6.562805743857641</v>
       </c>
       <c r="E4" t="n">
-        <v>12.55136630670771</v>
+        <v>2.039597024840003</v>
       </c>
       <c r="F4" t="n">
-        <v>10.059319468956</v>
+        <v>1.63463941370535</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.03438264752059</v>
+        <v>7.318087180222095</v>
       </c>
       <c r="D5" t="n">
-        <v>9.542819202694515</v>
+        <v>1.550708120437859</v>
       </c>
       <c r="E5" t="n">
-        <v>12.55136630670771</v>
+        <v>2.039597024840003</v>
       </c>
       <c r="F5" t="n">
-        <v>10.059319468956</v>
+        <v>1.63463941370535</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.60107523773828</v>
+        <v>3.02267472613247</v>
       </c>
       <c r="D6" t="n">
-        <v>22.93709015080274</v>
+        <v>3.727277149505446</v>
       </c>
       <c r="E6" t="n">
-        <v>12.55136630670771</v>
+        <v>2.039597024840003</v>
       </c>
       <c r="F6" t="n">
-        <v>10.059319468956</v>
+        <v>1.63463941370535</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.98793284300127</v>
+        <v>5.035539086987708</v>
       </c>
       <c r="D7" t="n">
-        <v>13.55802413205822</v>
+        <v>2.20317892145946</v>
       </c>
       <c r="E7" t="n">
-        <v>12.55136630670771</v>
+        <v>2.039597024840003</v>
       </c>
       <c r="F7" t="n">
-        <v>10.059319468956</v>
+        <v>1.63463941370535</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
